--- a/artfynd/A 57572-2021 artfynd.xlsx
+++ b/artfynd/A 57572-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57572-2021 artfynd.xlsx
+++ b/artfynd/A 57572-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>67010599</v>
       </c>
       <c r="B2" t="n">
-        <v>44328</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -732,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>370851.1122165406</v>
+        <v>370851</v>
       </c>
       <c r="R2" t="n">
-        <v>6382527.943011781</v>
+        <v>6382528</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -765,19 +760,9 @@
           <t>2017-08-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-08-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16869488</v>
+        <v>3047965</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,20 +817,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Olatorp, 490 m SV om, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>370907.7679674681</v>
+        <v>370908</v>
       </c>
       <c r="R3" t="n">
-        <v>6382550.829926004</v>
+        <v>6382551</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,26 +868,21 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-08-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-08-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>40 bladrosetter, ca 40 blomstjälkar, Enebacken</t>
         </is>
       </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
@@ -931,12 +912,7 @@
         <v>3063340</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>370851.1122165406</v>
+        <v>370851</v>
       </c>
       <c r="R4" t="n">
-        <v>6382527.943011781</v>
+        <v>6382528</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,19 +991,9 @@
           <t>2012-08-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-08-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,6 +1022,128 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>16900036</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Enebacken Ramslätt 450 m SO om, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>370832</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6382633</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fritsla</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>OV-Mar-0026</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2014-07-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2014-07-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lennart Walldén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lennart Walldén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
